--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_925_Canada_Pacific.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_925_Canada_Pacific.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R688d593e3133412f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R144cbc25ad0a4561"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rd6558f1b97404649"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rfa71591421a14dd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R1991ebb25368477c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R3ba2429f517f4ba9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R5f2466954cfb4d15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Re27fb55c821b4a9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R2d725ed38edf4b8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rd57030a5bd054e70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R06b92f34bd4d48d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R325d416b22af40bb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ925CommercialTable" displayName="EEZ925CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ925CommercialTable" displayName="EEZ925CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ925FunctionalTable" displayName="EEZ925FunctionalTable" ref="A1:O14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O14"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ925FunctionalTable" displayName="EEZ925FunctionalTable" ref="A1:E14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E14"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ925ValidationTable" displayName="EEZ925ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ925ValidationTable" displayName="EEZ925ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -2436,7 +2390,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09f736ec424246f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e12388efdae4fcb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2446,20 +2400,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -2467,552 +2411,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>106425.00000000061</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.303329386892174</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>2010.617169663911</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>106425.00000000061</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>2125.4350498171493</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$27,A2,'Species'!$U$2:$U$27))</x:f>
-        <x:v>226199425.1767914</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.303329386892174</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>2010.617169663911</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>213979932.28148296</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>12219492.895308435</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0571057891505178</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.05710578915051776</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>11149.7291557258</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.802328830663283</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>634.3498341594297</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>11149.7291557258</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>790.1342858997384</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$27,A3,'Species'!$U$2:$U$27))</x:f>
-        <x:v>8809783.284434898</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.802328830663283</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>634.3498341594297</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>7072828.84085722</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1736954.443577678</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.2455812918225744</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.24558129182257446</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>7799.3640497357</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.14</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1380.3842646028838</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>7799.3640497357</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1380.3842646028838</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$27,A4,'Species'!$U$2:$U$27))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>10766119.408164585</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.14</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1380.3842646028838</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>10766119.408164585</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>18903.0000000002</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.16</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>144.5439770745928</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>18903.0000000002</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$27,A5,'Species'!$U$2:$U$27))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2732314.7986410563</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.16</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>2732314.7986410563</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1727.4493450554</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.23</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>16.982436524617444</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1727.4493450554</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>16.982436524617444</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$27,A6,'Species'!$U$2:$U$27))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>29336.29885189531</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.23</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>16.982436524617444</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>29336.29885189531</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>25938.5185328088</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.153476836916876</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>142.38913014212784</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>25938.5185328088</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>162.71184034013524</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$27,A7,'Species'!$U$2:$U$27))</x:f>
-        <x:v>4220504.086170024</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.153476836916876</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>142.38913014212784</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>3693363.091062107</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>527140.9951079171</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1427265562878428</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.14272655628784287</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>9917.324634778599</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.094004416950844</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1241.664935763675</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>9917.324634778599</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1475.987594399255</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$27,A8,'Species'!$U$2:$U$27))</x:f>
-        <x:v>14637848.130563334</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.094004416950844</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1241.664935763675</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>12313994.25558988</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>2323853.8749734536</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.1887164982165352</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.1887164982165353</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>15810.217111705699</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.7554967914143838</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>569.5040165931304</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>15810.217111705699</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>578.7513910095814</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$27,A9,'Species'!$U$2:$U$27))</x:f>
-        <x:v>9150185.14556316</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.7554967914143838</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>569.5040165931304</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>9003982.148325836</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>146202.99723732285</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0162375929704066</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.01623759297040668</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>504</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.6858333333333335</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>485.10229954859045</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>504</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>498.85447815537043</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$27,A10,'Species'!$U$2:$U$27))</x:f>
-        <x:v>251422.65699030668</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.6858333333333335</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>485.10229954859045</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>244491.55897248958</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>6931.098017817101</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0283490278639722</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.028349027863972167</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdca1bdd7fa7b4717"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31c5ffa1a2ce4ee0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3022,20 +2607,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -3043,768 +2618,269 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>8592.4124165001</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.105034741503526</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1273.6049593119249</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>8592.4124165001</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1484.4384770990466</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$27,A2,'Species'!$U$2:$U$27))</x:f>
-        <x:v>12754907.602156347</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.105034741503526</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1273.6049593119249</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>10943339.066107888</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1811568.536048459</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1655407481304298</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.16554074813042982</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1295.2186604358</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.209109216184893</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1618.487002867333</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1295.2186604358</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1629.3798215381823</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$27,A3,'Species'!$U$2:$U$27))</x:f>
-        <x:v>2110403.1497938074</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.209109216184893</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1618.487002867333</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2096294.5677865802</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>14108.582007227233</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0067302478497209</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.006730247849720899</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>7799.3640497357</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.14</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1380.3842646028838</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>7799.3640497357</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1380.3842646028838</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$27,A4,'Species'!$U$2:$U$27))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>10766119.408164585</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.14</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1380.3842646028838</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>10766119.408164585</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>322</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.6100000000000003</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>407.380277804113</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>322</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>407.3802778041126</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$27,A5,'Species'!$U$2:$U$27))</x:f>
-        <x:v>131176.44945292425</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.6100000000000003</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>407.380277804113</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>131176.4494529244</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>-1.4551915228366852e-10</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>0.9999999999999989</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>-1.1093390078063618e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>2759.5369715936</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.79</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>616.5950018614822</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>2759.5369715936</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>616.5950018614822</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$27,A6,'Species'!$U$2:$U$27))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1701516.7041365847</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.79</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>616.5950018614822</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>1701516.7041365847</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>182</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.82</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>660.6934480075957</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>660.6934480075957</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$27,A7,'Species'!$U$2:$U$27))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>120246.20753738242</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.82</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>660.6934480075957</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>120246.20753738242</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>8335.7291557258</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1000</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>8335.7291557258</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$27,A8,'Species'!$U$2:$U$27))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>8335729.1557257995</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>8335729.1557257995</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>105933.0000000003</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.303995072357053</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2013.7014016379323</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>105933.0000000003</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2128.5932505412225</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$27,A9,'Species'!$U$2:$U$27))</x:f>
-        <x:v>225488268.80958396</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.303995072357053</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2013.7014016379323</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>213317430.5797117</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>12170838.229872257</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0570550573237112</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0570550573237113</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>34710.4518081267</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.4288664312654964</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>268.45186858950603</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>34710.4518081267</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>323.59779850724055</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$27,A10,'Species'!$U$2:$U$27))</x:f>
-        <x:v>11232225.790301468</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.4288664312654964</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>268.45186858950603</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>9318085.647477612</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1914140.1428238563</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.205422037877706</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.2054220378777062</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>19370.5635687876</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.1691723792913034</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>147.6292384001395</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>19370.5635687876</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>149.42447634991075</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$27,A11,'Species'!$U$2:$U$27))</x:f>
-        <x:v>2894436.317868745</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.1691723792913034</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>147.6292384001395</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>2859661.5470416015</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>34774.77082714345</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0121604498487309</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.012160449848730843</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>1164.8768538498</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.7551340267582227</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>569.0285105092192</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>1164.8768538498</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>583.4050307521321</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$27,A12,'Species'!$U$2:$U$27))</x:f>
-        <x:v>679595.0167426894</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.7551340267582227</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>569.0285105092192</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>662848.1410728171</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>16746.875669872272</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.025265026228734</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.02526502622873396</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>4895.4493450554</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>2.3374319565860766</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>21.748632589911246</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>4895.4493450554</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>22.114465571296446</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$27,A13,'Species'!$U$2:$U$27))</x:f>
-        <x:v>108260.24599725338</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>2.3374319565860766</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>21.748632589911246</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>106469.32916813153</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>1790.916829121852</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0168209647145772</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.016820964714577263</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>2814</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.2167803837953093</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>164.73291512243483</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>2814</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>168.46273230600463</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$27,A14,'Species'!$U$2:$U$27))</x:f>
-        <x:v>474054.128709097</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.2167803837953093</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>164.73291512243483</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>463558.4231545316</x:v>
       </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>10495.705554565357</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0226416025042577</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.02264160250425762</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G14">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O14">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd90d07e137fd4217"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b12694ec7d943c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3979,7 +3055,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -4078,7 +3154,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>276796938.98617065</x:v>
+        <x:v>259836362.681948</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -4092,7 +3168,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>276796938.98617065</x:v>
+        <x:v>260822475.22653812</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -4106,7 +3182,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-16960576.304222643</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -4120,7 +3196,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-15974463.759632528</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -4131,9 +3207,9 @@
         <x:v>EEZ_925</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -4145,47 +3221,19 @@
         <x:v>EEZ_925</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_925</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_925</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb61089afb99741f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99ab06db6abd49cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4232,7 +3280,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
